--- a/data/novedades/Modificados_posgrado.xlsx
+++ b/data/novedades/Modificados_posgrado.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,107 +530,920 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CÓDIGO_INSTITUCIÓN_ANTERIOR</t>
+          <t>PROGINSTI</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>NOMBRE_INSTITUCIÓN_ANTERIOR</t>
+          <t>NÚMERO_CRÉDITOS_NUEVOS</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SECTOR_ANTERIOR</t>
+          <t>NÚMERO_CRÉDITOS_ANTERIORES</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO_OFERTA_PROGRAMA_ANTERIOR</t>
+          <t>FECHA_OBTENCION</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>MUNICIPIO_OFERTA_PROGRAMA_ANTERIOR</t>
+          <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>NOMBRE_DEL_PROGRAMA_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>MODALIDAD_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>NÚMERO_CRÉDITOS_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>NÚMERO_PERIODOS_DE_DURACIÓN_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>PERIODICIDAD_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>COSTO_MATRÍCULA_ESTUD_NUEVOS_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>PERIODICIDAD_ADMISIONES_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA_DE_REGISTRO_EN_SNIES_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_AMPLIO_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>CINE_F_2013_AC_CAMPO_DETALLADO_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>NIVEL_DE_FORMACIÓN_ANTERIOR</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA_DETECCION</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>DIVISIÓN UNINORTE</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6569</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN CARDIOLOGIA PEDIATRICA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>121</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>31697659</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>44572</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6569-121</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>130</v>
+      </c>
+      <c r="V2" t="n">
+        <v>121</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>104918</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIRUGIA DE MANO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>29503364</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>44755</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>104918-54</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>64</v>
+      </c>
+      <c r="V3" t="n">
+        <v>54</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ENDOCRINOLOGIA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>114</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>31697659</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>44299</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1319-114</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>97</v>
+      </c>
+      <c r="V4" t="n">
+        <v>114</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1305</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GINECOLOGIA Y OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>208</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>31697659</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>44295</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1305-208</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>270</v>
+      </c>
+      <c r="V5" t="n">
+        <v>208</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>104922</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN MASTOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>117</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>29503364</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>44725</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>104922-117</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>104</v>
+      </c>
+      <c r="V6" t="n">
+        <v>117</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>16130</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN MEDICINA MATERNO FETAL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>27306068</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>44671</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>16130-125</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>130</v>
+      </c>
+      <c r="V7" t="n">
+        <v>125</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1308</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN NEFROLOGIA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>119</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>31697659</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>44299</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1308-119</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>119</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1315</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>282</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>31697659</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>44292</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1315-282</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>182</v>
+      </c>
+      <c r="V9" t="n">
+        <v>282</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Activo</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Modificados_posgrado.xlsx
+++ b/data/novedades/Modificados_posgrado.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,127 +421,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NIVEL_DE_FORMACIÓN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS_NUEVOS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS_ANTERIORES</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -615,7 +603,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>44572</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -726,7 +714,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>44755</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -837,7 +825,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>44299</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -948,7 +936,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -1059,7 +1047,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>44725</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1170,7 +1158,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>44671</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1281,7 +1269,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>44299</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1392,7 +1380,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>44292</v>
       </c>
       <c r="O9" t="inlineStr">

--- a/data/novedades/Modificados_posgrado.xlsx
+++ b/data/novedades/Modificados_posgrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:AR14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +549,101 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>CÓDIGO_INSTITUCIÓN_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>NOMBRE_INSTITUCIÓN_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>SECTOR_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO_OFERTA_PROGRAMA_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>MUNICIPIO_OFERTA_PROGRAMA_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>NOMBRE_DEL_PROGRAMA_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>MODALIDAD_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>NÚMERO_CRÉDITOS_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>NÚMERO_PERIODOS_DE_DURACIÓN_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>PERIODICIDAD_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>COSTO_MATRÍCULA_ESTUD_NUEVOS_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>PERIODICIDAD_ADMISIONES_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>FECHA_DE_REGISTRO_EN_SNIES_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>CINE_F_2013_AC_CAMPO_AMPLIO_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>CINE_F_2013_AC_CAMPO_DETALLADO_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>NIVEL_DE_FORMACIÓN_ANTERIOR</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>QUE_CAMBIO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -657,6 +755,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -768,6 +885,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -879,6 +1015,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -990,6 +1145,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1101,6 +1275,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1212,6 +1405,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1323,6 +1535,25 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1432,6 +1663,985 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>106769</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN CULTURAL Y CREATIVA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>19659700</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN CULTURAL Y CREATIVA</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19659700</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>43160</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>NÚMERO_CRÉDITOS: 23 → 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>116219</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Maestría en Filosofía y Justicia Social</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>41</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>8590000</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>45197</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Filosofía y ética</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Maestría en Filosofía y Justicia Social</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>41</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>8590000</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>45197</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Filosofía y ética</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>MODALIDAD: Presencial → Virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>104770</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN INGENIERIA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>11221999</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN INGENIERIA</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>11221999</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>42211</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>NÚMERO_CRÉDITOS: 50 → 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CES</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3460</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN AUDITORIA EN SALUD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>11034202</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CES</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN AUDITORIA EN SALUD</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>11034202</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>MODALIDAD: Presencial → Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REPUBLICANA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>90648</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN REVISORIA FISCAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>26</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>6598700</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REPUBLICANA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN REVISORIA FISCAL</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6598700</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>40386</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>NÚMERO_CRÉDITOS: 30 → 26</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Modificados_posgrado.xlsx
+++ b/data/novedades/Modificados_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR14"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1686,10 +1686,8 @@
       <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1728</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1743,7 +1741,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1789,10 +1787,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="Z10" t="n">
+        <v>1728</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1843,7 +1839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL10" s="2" t="n">
+      <c r="AL10" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1878,10 +1874,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1803</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1935,7 +1929,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="1" t="n">
         <v>45197</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1981,10 +1975,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="Z11" t="n">
+        <v>1803</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -2035,7 +2027,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL11" s="2" t="n">
+      <c r="AL11" s="1" t="n">
         <v>45197</v>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2070,10 +2062,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1825</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2127,7 +2117,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="1" t="n">
         <v>46060</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -2173,10 +2163,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="Z12" t="n">
+        <v>1825</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2227,7 +2215,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL12" s="2" t="n">
+      <c r="AL12" s="1" t="n">
         <v>42211</v>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2262,10 +2250,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="A13" t="n">
+        <v>2708</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2319,7 +2305,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -2365,10 +2351,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="Z13" t="n">
+        <v>2708</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2419,7 +2403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL13" s="2" t="n">
+      <c r="AL13" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2454,10 +2438,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2837</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2511,7 +2493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -2557,10 +2539,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
+      <c r="Z14" t="n">
+        <v>2837</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2611,7 +2591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL14" s="2" t="n">
+      <c r="AL14" s="1" t="n">
         <v>40386</v>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2642,6 +2622,198 @@
       <c r="AR14" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS: 30 → 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>51633</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN MEDICINA CRITICA Y CUIDADO INTENSIVO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>308</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>24170314</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>38589</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN MEDICINA CRITICA Y CUIDADO INTENSIVO</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>325</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24170314</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="n">
+        <v>38589</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>NÚMERO_CRÉDITOS: 325 → 308</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Modificados_posgrado.xlsx
+++ b/data/novedades/Modificados_posgrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2626,10 +2623,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1711</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2683,7 +2678,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>38589</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -2729,10 +2724,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="Z15" t="n">
+        <v>1711</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2783,7 +2776,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL15" s="2" t="n">
+      <c r="AL15" s="1" t="n">
         <v>38589</v>
       </c>
       <c r="AM15" t="inlineStr">
